--- a/device_registry.xlsx
+++ b/device_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,134 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>09:08:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FpGfctVovDpk</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>192.168.3.10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10:10:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5FwF6dZFSKm6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>192.168.3.10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10:30:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000002</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>JtiMWo9ujtL4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>192.168.3.10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10:37:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000002</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>x2xknVHuy29y</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>192.168.3.10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10:39:44</t>
         </is>
       </c>
     </row>

--- a/device_registry.xlsx
+++ b/device_registry.xlsx
@@ -1,34 +1,123 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29816"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEFE7EBF-9628-4A92-9BCE-C9B9C0D628AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+  <si>
+    <t>UID</t>
+  </si>
+  <si>
+    <t>MQTT User</t>
+  </si>
+  <si>
+    <t>MQTT Password</t>
+  </si>
+  <si>
+    <t>MQTT Server</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>CVL-TS1-26-000001</t>
+  </si>
+  <si>
+    <t>3zP5dPLJMEj2</t>
+  </si>
+  <si>
+    <t>db4e59e7f86a44c983d9421fafb04bcd.s1.eu.hivemq.cloud</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>10:25:59</t>
+  </si>
+  <si>
+    <t>CVL-TS1-26-000002</t>
+  </si>
+  <si>
+    <t>ESfju93Kt8vL</t>
+  </si>
+  <si>
+    <t>10:27:14</t>
+  </si>
+  <si>
+    <t>CVL-TS1-26-000003</t>
+  </si>
+  <si>
+    <t>5zpR6dEeASPL</t>
+  </si>
+  <si>
+    <t>10:28:10</t>
+  </si>
+  <si>
+    <t>CVL-TS1-26-000004</t>
+  </si>
+  <si>
+    <t>TTYKPQeNH8Sa</t>
+  </si>
+  <si>
+    <t>10:29:16</t>
+  </si>
+  <si>
+    <t>CVL-TS1-26-000005</t>
+  </si>
+  <si>
+    <t>pKfun7BrLH2X</t>
+  </si>
+  <si>
+    <t>10:34:21</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +136,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,204 +438,136 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>UID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>MQTT User</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>MQTT Password</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>MQTT Server</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CVL-TS1-26-000001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CVL-TS1-26-000001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>bEkbtc8Ued8y</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>192.168.3.10</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>09:08:24</t>
-        </is>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CVL-TS1-26-000002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CVL-TS1-26-000002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>FpGfctVovDpk</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>192.168.3.10</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10:10:42</t>
-        </is>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CVL-TS1-26-000001</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CVL-TS1-26-000001</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>5FwF6dZFSKm6</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>192.168.3.10</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10:30:38</t>
-        </is>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CVL-TS1-26-000002</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CVL-TS1-26-000002</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>JtiMWo9ujtL4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>192.168.3.10</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10:37:33</t>
-        </is>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CVL-TS1-26-000002</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CVL-TS1-26-000002</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>x2xknVHuy29y</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>192.168.3.10</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>10:39:44</t>
-        </is>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/device_registry.xlsx
+++ b/device_registry.xlsx
@@ -1,123 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29816"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEFE7EBF-9628-4A92-9BCE-C9B9C0D628AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
-  <si>
-    <t>UID</t>
-  </si>
-  <si>
-    <t>MQTT User</t>
-  </si>
-  <si>
-    <t>MQTT Password</t>
-  </si>
-  <si>
-    <t>MQTT Server</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>CVL-TS1-26-000001</t>
-  </si>
-  <si>
-    <t>3zP5dPLJMEj2</t>
-  </si>
-  <si>
-    <t>db4e59e7f86a44c983d9421fafb04bcd.s1.eu.hivemq.cloud</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>10:25:59</t>
-  </si>
-  <si>
-    <t>CVL-TS1-26-000002</t>
-  </si>
-  <si>
-    <t>ESfju93Kt8vL</t>
-  </si>
-  <si>
-    <t>10:27:14</t>
-  </si>
-  <si>
-    <t>CVL-TS1-26-000003</t>
-  </si>
-  <si>
-    <t>5zpR6dEeASPL</t>
-  </si>
-  <si>
-    <t>10:28:10</t>
-  </si>
-  <si>
-    <t>CVL-TS1-26-000004</t>
-  </si>
-  <si>
-    <t>TTYKPQeNH8Sa</t>
-  </si>
-  <si>
-    <t>10:29:16</t>
-  </si>
-  <si>
-    <t>CVL-TS1-26-000005</t>
-  </si>
-  <si>
-    <t>pKfun7BrLH2X</t>
-  </si>
-  <si>
-    <t>10:34:21</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -136,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -438,136 +407,276 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
-    <col min="2" max="2" width="26.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col width="28.5703125" customWidth="1" min="1" max="1"/>
+    <col width="26.5703125" customWidth="1" min="2" max="2"/>
+    <col width="19.42578125" customWidth="1" min="3" max="3"/>
+    <col width="23.5703125" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="25.42578125" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>UID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>MQTT User</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MQTT Password</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>MQTT Server</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3zP5dPLJMEj2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>db4e59e7f86a44c983d9421fafb04bcd.s1.eu.hivemq.cloud</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10:25:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ESfju93Kt8vL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>db4e59e7f86a44c983d9421fafb04bcd.s1.eu.hivemq.cloud</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10:27:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5zpR6dEeASPL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>db4e59e7f86a44c983d9421fafb04bcd.s1.eu.hivemq.cloud</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10:28:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TTYKPQeNH8Sa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>db4e59e7f86a44c983d9421fafb04bcd.s1.eu.hivemq.cloud</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10:29:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>pKfun7BrLH2X</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>db4e59e7f86a44c983d9421fafb04bcd.s1.eu.hivemq.cloud</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10:34:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yq37XUiCU9MC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>db4e59e7f86a44c983d9421fafb04bcd.s1.eu.hivemq.cloud</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>11:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000006</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CVL-TS1-26-000006</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>kGKDy92QL2Yt</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>db4e59e7f86a44c983d9421fafb04bcd.s1.eu.hivemq.cloud</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>11:18:13</t>
+        </is>
       </c>
     </row>
   </sheetData>
